--- a/Journal Trades.xlsx
+++ b/Journal Trades.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="H1" s="3">
         <f>NOW()</f>
-        <v>45817.75656</v>
+        <v>45817.75979</v>
       </c>
     </row>
     <row r="2">
@@ -2687,7 +2687,7 @@
         <v>0.4511</v>
       </c>
       <c r="G51" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
